--- a/project/Template12_NoStamp.xlsx
+++ b/project/Template12_NoStamp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\Rev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAB5966-FE38-4077-A3D2-4F8C67D12A6D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B95CDA-1EFA-421E-969F-2BD59DFE3906}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
     <t>Novia Auni Azalia</t>
   </si>
   <si>
-    <t>Jl. Margonda Raya No.518G, Pondok Cina, Beji, Kota Depok</t>
+    <t>Jl. Margonda Raya No.514F, Pondok Cina, Beji, Kota Depok</t>
   </si>
 </sst>
 </file>
